--- a/data/trans_dic/P15E_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,17; 81,52</t>
+          <t>28,81; 84,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,83; 84,61</t>
+          <t>35,14; 81,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,24; 100,0</t>
+          <t>29,87; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 87,83</t>
+          <t>15,42; 88,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,07; 82,57</t>
+          <t>33,84; 83,53</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 85,08</t>
+          <t>9,35; 88,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,21; 83,67</t>
+          <t>23,85; 81,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 75,3</t>
+          <t>29,7; 76,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,88; 81,11</t>
+          <t>42,08; 81,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 89,8</t>
+          <t>53,02; 90,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,06; 81,39</t>
+          <t>52,31; 80,04</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,57; 91,52</t>
+          <t>42,2; 92,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,77; 89,92</t>
+          <t>69,36; 89,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,01; 87,85</t>
+          <t>67,34; 87,96</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58,21; 82,99</t>
+          <t>59,8; 83,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,21; 82,99</t>
+          <t>59,8; 83,07</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50,81; 77,09</t>
+          <t>50,3; 76,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>64,61; 78,8</t>
+          <t>65,51; 79,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,84; 76,36</t>
+          <t>63,49; 76,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1435; 4647</t>
+          <t>1642; 4811</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2746; 6869</t>
+          <t>2853; 6651</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1571; 5196</t>
+          <t>1552; 5196</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>566; 3258</t>
+          <t>572; 3267</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2945; 7352</t>
+          <t>3013; 7438</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>323; 3159</t>
+          <t>347; 3301</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1634; 5026</t>
+          <t>1433; 4871</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2907; 7319</t>
+          <t>2887; 7431</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6387; 12372</t>
+          <t>6419; 12412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6332; 10219</t>
+          <t>6033; 10255</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14132; 21676</t>
+          <t>13932; 21315</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2634; 6093</t>
+          <t>2809; 6175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16859; 22043</t>
+          <t>17003; 22055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21199; 27385</t>
+          <t>20992; 27418</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17278; 24629</t>
+          <t>17748; 24653</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17278; 24629</t>
+          <t>17748; 24653</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16887; 25623</t>
+          <t>16719; 25485</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>52329; 63820</t>
+          <t>53053; 64572</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72916; 87222</t>
+          <t>72525; 87039</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15E_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 100,0</t>
+          <t>18,73; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,81; 84,41</t>
+          <t>31,79; 84,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,14; 81,91</t>
+          <t>41,08; 85,81</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,87; 100,0</t>
+          <t>28,78; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 88,1</t>
+          <t>14,03; 85,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,84; 83,53</t>
+          <t>34,06; 85,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>49,8%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 88,9</t>
+          <t>8,27; 83,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,85; 81,08</t>
+          <t>25,63; 81,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,7; 76,45</t>
+          <t>27,17; 71,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,08; 81,37</t>
+          <t>40,65; 80,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,02; 90,12</t>
+          <t>56,65; 91,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,31; 80,04</t>
+          <t>54,55; 81,98</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,2; 92,76</t>
+          <t>43,3; 92,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,36; 89,97</t>
+          <t>70,75; 90,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67,34; 87,96</t>
+          <t>67,55; 87,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,8; 83,07</t>
+          <t>61,85; 84,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,8; 83,07</t>
+          <t>61,85; 84,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50,3; 76,68</t>
+          <t>51,23; 76,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65,51; 79,73</t>
+          <t>65,79; 79,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,49; 76,2</t>
+          <t>63,67; 76,47</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>6943</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>143; 2419</t>
+          <t>589; 3142</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1642; 4811</t>
+          <t>2258; 6018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2853; 6651</t>
+          <t>4209; 8790</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5899</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1552; 5196</t>
+          <t>1666; 5787</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>572; 3267</t>
+          <t>557; 3397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3013; 7438</t>
+          <t>3324; 8305</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5469</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>347; 3301</t>
+          <t>363; 3654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1433; 4871</t>
+          <t>1689; 5359</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2887; 7431</t>
+          <t>2983; 7841</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>19684</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6419; 12412</t>
+          <t>6719; 13347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6033; 10255</t>
+          <t>6865; 11057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13932; 21315</t>
+          <t>15626; 23483</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>21100</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>25937</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2809; 6175</t>
+          <t>2944; 6299</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17003; 22055</t>
+          <t>18269; 23342</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20992; 27418</t>
+          <t>22035; 28594</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>23250</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17748; 24653</t>
+          <t>19431; 26465</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17748; 24653</t>
+          <t>19431; 26465</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>63586</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79846</t>
+          <t>87182</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16719; 25485</t>
+          <t>18774; 28102</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53053; 64572</t>
+          <t>57248; 69519</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72525; 87039</t>
+          <t>78736; 94571</t>
         </is>
       </c>
     </row>
